--- a/data/hub_prioritization_results.xlsx
+++ b/data/hub_prioritization_results.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ohad\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BA4317D5-0DB8-42B9-8DD4-503D75A24919}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3401101F-91EA-40B4-8CC1-023A2052C64D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D269891B-4ECE-4013-B554-94370F5A8FDB}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D269891B-4ECE-4013-B554-94370F5A8FDB}"/>
   </bookViews>
   <sheets>
     <sheet name="hubs_final_results_20260617_124" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2191" uniqueCount="901">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2200" uniqueCount="910">
   <si>
     <t>group</t>
   </si>
@@ -2723,6 +2736,33 @@
   </si>
   <si>
     <t>RankByHubTypeMetro</t>
+  </si>
+  <si>
+    <t>מנחם בגין/הבוצרים, אשקלון</t>
+  </si>
+  <si>
+    <t>מנחם בגין/אקסודוס, אשקלון</t>
+  </si>
+  <si>
+    <t>יצחק רבין/מנחם בגין, אשקלון</t>
+  </si>
+  <si>
+    <t>יצחק רבין/עמק יזרעאל, אשקלון</t>
+  </si>
+  <si>
+    <t>א.ת דרומי, אשקלון</t>
+  </si>
+  <si>
+    <t>בן גוריון/התעשייה, אשקלון</t>
+  </si>
+  <si>
+    <t>תחנת רכבת קרית גת</t>
+  </si>
+  <si>
+    <t>תחנת רכבת ירושלים-החאן</t>
+  </si>
+  <si>
+    <t>תחנת רכבת נתניה</t>
   </si>
 </sst>
 </file>
@@ -3267,6 +3307,87 @@
 </styleSheet>
 </file>
 
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B208A03B-F993-4E48-9968-E2EE818B01D7}" name="טבלה1" displayName="טבלה1" ref="A1:BR143" totalsRowShown="0">
+  <autoFilter ref="A1:BR143" xr:uid="{B208A03B-F993-4E48-9968-E2EE818B01D7}"/>
+  <tableColumns count="70">
+    <tableColumn id="1" xr3:uid="{9D3F6445-E07F-4B96-B680-8139C4974D78}" name="group"/>
+    <tableColumn id="2" xr3:uid="{136D5821-1F29-47AC-ACED-D38E96EE3BA7}" name="x"/>
+    <tableColumn id="3" xr3:uid="{B7D7AEE0-7B78-4C58-9C0F-16C590A76296}" name="y"/>
+    <tableColumn id="4" xr3:uid="{4D2A3D89-E5CC-41A9-8EE4-58341B670E79}" name="h3_index"/>
+    <tableColumn id="5" xr3:uid="{8A906EFF-FD82-4111-9DEA-934B9D1A176D}" name="node"/>
+    <tableColumn id="6" xr3:uid="{058D4DEB-4461-46A3-AD1B-8F14FA068E9C}" name="Mode_Planned"/>
+    <tableColumn id="7" xr3:uid="{26EEF4BC-71A7-446A-8174-4D39B50AD6E3}" name="Modes_ForPlot"/>
+    <tableColumn id="8" xr3:uid="{AC642577-316D-4C59-8D30-CA6E044A114E}" name="Line_Unique"/>
+    <tableColumn id="9" xr3:uid="{8B2107D5-74DB-45C6-AD76-2457E8E7844D}" name="Line_Names"/>
+    <tableColumn id="10" xr3:uid="{F5D3C4F8-0938-47D4-A150-15AB43F26A60}" name="address"/>
+    <tableColumn id="11" xr3:uid="{A3BCD7FB-CC2E-4988-B0C7-B8942A335967}" name="area"/>
+    <tableColumn id="12" xr3:uid="{188D48B4-7CEE-4137-B758-76D6A82C68FA}" name="Metro"/>
+    <tableColumn id="13" xr3:uid="{04EAFBC4-C585-4D2A-942F-F32AFCEAA51F}" name="location"/>
+    <tableColumn id="14" xr3:uid="{2870CF9B-457D-4EF5-AC9B-31245694FF35}" name="LocationForChart"/>
+    <tableColumn id="15" xr3:uid="{738540D2-FDEF-4160-BEC3-4E7A3F33E34C}" name="TotalDemand"/>
+    <tableColumn id="16" xr3:uid="{4A1BD0A3-4204-45E9-8693-CD8A951B20EE}" name="TotalTransfers"/>
+    <tableColumn id="17" xr3:uid="{BDD2C467-7FCB-4824-BAFC-31348BCC80AF}" name="TransferRate"/>
+    <tableColumn id="18" xr3:uid="{5EC59DC5-D12E-42D7-8DE1-28FF9292D3DD}" name="BRT Lines"/>
+    <tableColumn id="19" xr3:uid="{825BA5D6-DA61-4631-851F-F416C8F084AC}" name="Cable Line Lines"/>
+    <tableColumn id="20" xr3:uid="{15B89615-C8FC-4C64-A545-129E3CE04669}" name="Funicular Lines"/>
+    <tableColumn id="21" xr3:uid="{12AF16D7-CD4B-4EAF-A36F-328C9BF3F81B}" name="HighSpeed Rail Lines"/>
+    <tableColumn id="22" xr3:uid="{BA7391F1-2687-476E-99F5-3A659C59FCDE}" name="Interurban Rail Lines"/>
+    <tableColumn id="23" xr3:uid="{5E05DD92-5E17-4308-869D-61CA6569EF84}" name="LRT Lines"/>
+    <tableColumn id="24" xr3:uid="{70B9CFD6-3791-4508-9183-66E92E34BA08}" name="Metro Lines"/>
+    <tableColumn id="25" xr3:uid="{E73737B1-4459-43F6-AF74-8A877FFB4FA2}" name="Suburban Rail Lines"/>
+    <tableColumn id="26" xr3:uid="{35532B16-2B9A-4239-BA68-43744554DFAC}" name="pop_0_500"/>
+    <tableColumn id="27" xr3:uid="{828A712B-90E1-4519-9078-8F4B79BD7596}" name="emp_0_500"/>
+    <tableColumn id="28" xr3:uid="{5133CF32-3EDC-43B0-A072-20E7F742F0F8}" name="pop_500_1000"/>
+    <tableColumn id="29" xr3:uid="{464EE57F-5C3C-43F3-B46A-964C4A473996}" name="emp_500_1000"/>
+    <tableColumn id="30" xr3:uid="{17BA8FFA-816A-4CF5-AEF1-0F71CC13A58E}" name="pop_1000_1500"/>
+    <tableColumn id="31" xr3:uid="{1FEC42BF-0372-4BB4-BB0A-14282A597579}" name="emp_1000_1500"/>
+    <tableColumn id="32" xr3:uid="{7B3BBDCD-A9CC-48AF-94BC-EF946E1F219C}" name="TotalPop_2050"/>
+    <tableColumn id="33" xr3:uid="{1B97B887-D2A1-4D7D-A1F3-B997EBFB4EB6}" name="TotalEmp_2050"/>
+    <tableColumn id="34" xr3:uid="{362F9812-F23B-4DD1-BC15-8E881372F562}" name="Region_category"/>
+    <tableColumn id="35" xr3:uid="{35AD6169-6DBE-4D46-AD05-A0EBC5130AA2}" name="Location_category"/>
+    <tableColumn id="36" xr3:uid="{D3A69D28-5F33-4DAD-8E24-8BEED6223DB6}" name="RegionLocation"/>
+    <tableColumn id="37" xr3:uid="{2107034B-5174-466E-8999-8F62B582E33D}" name="Num_Modes"/>
+    <tableColumn id="38" xr3:uid="{EF134249-E568-4D90-BE0C-4289BBED60B2}" name="score"/>
+    <tableColumn id="39" xr3:uid="{109A4BF6-4DF1-41BD-A26A-83C44CE169B4}" name=" "/>
+    <tableColumn id="40" xr3:uid="{F1800A47-3755-4989-A21A-62DFD0C79EED}" name="HubType"/>
+    <tableColumn id="41" xr3:uid="{A596EE36-D1F9-4EC8-9136-310318C0EDE0}" name="HubType_Filtered"/>
+    <tableColumn id="42" xr3:uid="{D8D14577-145C-4506-B34E-11C8DB0D9B28}" name="HubTypeHE"/>
+    <tableColumn id="43" xr3:uid="{61C72ED1-92C4-46B9-A313-E732DAB0642C}" name="BusTERMINAL_Clone"/>
+    <tableColumn id="44" xr3:uid="{65AEA195-F32C-4683-8F29-5B34911C87A3}" name="RegionLocation_Norm"/>
+    <tableColumn id="45" xr3:uid="{B3068C32-D45B-4970-89D6-4AA73AB57B80}" name="score_Norm"/>
+    <tableColumn id="46" xr3:uid="{29AC560B-CF15-4693-B397-5D3B6C3A64D1}" name="bus_terminal_Norm"/>
+    <tableColumn id="47" xr3:uid="{F4B76EEE-7A18-449A-B81A-8479A124259C}" name="TotalDemand_Norm"/>
+    <tableColumn id="48" xr3:uid="{5F3BCD6B-E195-405F-B98D-EC6BE946CB7A}" name="PopEmp_Score_Norm"/>
+    <tableColumn id="49" xr3:uid="{6E2696EF-80CA-40CB-80F6-7444F27A4CC9}" name="TotalScore_MC"/>
+    <tableColumn id="50" xr3:uid="{F01FED49-F570-4064-BF06-3F0989F25561}" name="Rank_TS_MC"/>
+    <tableColumn id="51" xr3:uid="{A61D8549-F9C0-4890-A255-CFADFBDF6F75}" name="Rank_By_TS_MC_By_Metro"/>
+    <tableColumn id="52" xr3:uid="{0D29B95C-9CC2-4894-B809-28D604F8F9B2}" name="TotalNumLines"/>
+    <tableColumn id="53" xr3:uid="{5BFAD6B4-7B30-492B-91A4-56DEB44A7DDE}" name="NumLinesStatus_0"/>
+    <tableColumn id="54" xr3:uid="{E53BEDBF-B0E3-4FFB-B00F-36CC3AC1B83C}" name="NumLinesStatus_1"/>
+    <tableColumn id="55" xr3:uid="{5EE44A42-3B55-4F62-AD3B-8FCE38D8E87B}" name="NumLinesStatus_2"/>
+    <tableColumn id="56" xr3:uid="{0D9B9947-BB4B-4585-AABE-BCAA3E34A90A}" name="NumLinesStatus_3"/>
+    <tableColumn id="57" xr3:uid="{8664969C-B976-4FC5-ADF3-56C72CE839CC}" name="NumLinesStatus_4"/>
+    <tableColumn id="58" xr3:uid="{2B928455-0E03-4C13-AFB6-61D2587E64EA}" name="NumLinesStatus_5"/>
+    <tableColumn id="59" xr3:uid="{2A3BB36B-48BB-4789-802E-C7969E5D1059}" name="NumLinesStatus_6"/>
+    <tableColumn id="60" xr3:uid="{B1502701-F95A-4921-8B2E-12FAEDD772AA}" name="NumLinesStatus_7"/>
+    <tableColumn id="61" xr3:uid="{4F7290BA-74E8-4CA8-BA9C-F1E132DF4CBD}" name="TotalLinesAllStatuses"/>
+    <tableColumn id="62" xr3:uid="{FD814297-4639-4B2A-B762-92407F98351E}" name="Line_Nunique"/>
+    <tableColumn id="63" xr3:uid="{75BFD955-5783-4777-AA43-538A1B2F60D5}" name="Average_Simulated_Score"/>
+    <tableColumn id="64" xr3:uid="{749AAC74-D3FA-45D7-A8CB-F592112C260F}" name="Overall_Rank"/>
+    <tableColumn id="65" xr3:uid="{6BFC5937-DF55-47CE-B860-4DD7D323F419}" name="Rank_within_HubType"/>
+    <tableColumn id="66" xr3:uid="{819C9C01-A7EB-485B-B161-664D9E35A159}" name="LogDemand"/>
+    <tableColumn id="67" xr3:uid="{9E23AD31-BF94-497A-9A8E-923537836FE6}" name="PopEmp_Score"/>
+    <tableColumn id="68" xr3:uid="{0E12B9C9-1107-40A5-BFBC-2200AAF350B1}" name="HubNameHE"/>
+    <tableColumn id="69" xr3:uid="{F73E6539-6E4E-426B-A040-750916472A54}" name="Line_Names_forPlot"/>
+    <tableColumn id="70" xr3:uid="{2D6157C1-A055-46DD-8656-EC8D65BD6AA7}" name="RankByHubTypeMetro">
+      <calculatedColumnFormula>IF($AP2="ארצי",COUNTIFS($AP$2:$AP$143,$AP2,$BK$2:$BK$143,"&gt;"&amp;$BK2)+1,COUNTIFS($AP$2:$AP$143,$AP2,$L$2:$L$143,$L2,$BK$2:$BK$143,"&gt;"&amp;$BK2)+1)</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ערכת נושא Office">
   <a:themeElements>
@@ -3608,6 +3729,67 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0E88CDC-6037-4F86-8BE9-CEB57E3DE4EC}">
   <dimension ref="A1:BR143"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="3" width="9.140625" customWidth="1"/>
+    <col min="4" max="4" width="11.140625" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" customWidth="1"/>
+    <col min="6" max="6" width="16.28515625" customWidth="1"/>
+    <col min="7" max="7" width="16.42578125" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" customWidth="1"/>
+    <col min="9" max="9" width="14.140625" customWidth="1"/>
+    <col min="10" max="10" width="10.28515625" customWidth="1"/>
+    <col min="11" max="12" width="9.140625" customWidth="1"/>
+    <col min="13" max="13" width="10.42578125" customWidth="1"/>
+    <col min="14" max="14" width="18.7109375" customWidth="1"/>
+    <col min="15" max="15" width="15.140625" customWidth="1"/>
+    <col min="16" max="16" width="16" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" customWidth="1"/>
+    <col min="18" max="18" width="11.85546875" customWidth="1"/>
+    <col min="19" max="19" width="18" customWidth="1"/>
+    <col min="20" max="20" width="16.7109375" customWidth="1"/>
+    <col min="21" max="21" width="22.140625" customWidth="1"/>
+    <col min="22" max="22" width="21.7109375" customWidth="1"/>
+    <col min="23" max="23" width="11.7109375" customWidth="1"/>
+    <col min="24" max="24" width="13.7109375" customWidth="1"/>
+    <col min="25" max="25" width="20.85546875" customWidth="1"/>
+    <col min="26" max="26" width="12.28515625" customWidth="1"/>
+    <col min="27" max="27" width="12.85546875" customWidth="1"/>
+    <col min="28" max="28" width="15.28515625" customWidth="1"/>
+    <col min="29" max="29" width="15.85546875" customWidth="1"/>
+    <col min="30" max="30" width="16.28515625" customWidth="1"/>
+    <col min="31" max="31" width="16.85546875" customWidth="1"/>
+    <col min="32" max="32" width="15.85546875" customWidth="1"/>
+    <col min="33" max="33" width="16.42578125" customWidth="1"/>
+    <col min="34" max="34" width="18" customWidth="1"/>
+    <col min="35" max="35" width="19.42578125" customWidth="1"/>
+    <col min="36" max="36" width="17.140625" customWidth="1"/>
+    <col min="37" max="37" width="14.28515625" customWidth="1"/>
+    <col min="38" max="39" width="9.140625" customWidth="1"/>
+    <col min="40" max="40" width="11.140625" customWidth="1"/>
+    <col min="41" max="41" width="19" customWidth="1"/>
+    <col min="42" max="42" width="13.7109375" customWidth="1"/>
+    <col min="43" max="43" width="21.85546875" customWidth="1"/>
+    <col min="44" max="44" width="23" customWidth="1"/>
+    <col min="45" max="45" width="14" customWidth="1"/>
+    <col min="46" max="46" width="20.7109375" customWidth="1"/>
+    <col min="47" max="47" width="21" customWidth="1"/>
+    <col min="48" max="48" width="22.42578125" customWidth="1"/>
+    <col min="49" max="49" width="16.5703125" customWidth="1"/>
+    <col min="50" max="50" width="14.42578125" customWidth="1"/>
+    <col min="51" max="51" width="26.5703125" customWidth="1"/>
+    <col min="52" max="52" width="16.7109375" customWidth="1"/>
+    <col min="53" max="60" width="19.85546875" customWidth="1"/>
+    <col min="61" max="61" width="22.5703125" customWidth="1"/>
+    <col min="62" max="62" width="15.5703125" customWidth="1"/>
+    <col min="63" max="63" width="26.28515625" customWidth="1"/>
+    <col min="64" max="64" width="14.85546875" customWidth="1"/>
+    <col min="65" max="65" width="22.85546875" customWidth="1"/>
+    <col min="66" max="66" width="13.85546875" customWidth="1"/>
+    <col min="67" max="67" width="16.5703125" customWidth="1"/>
+    <col min="68" max="68" width="14.7109375" customWidth="1"/>
+    <col min="69" max="69" width="21.140625" customWidth="1"/>
+    <col min="70" max="70" width="23" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -5301,6 +5483,9 @@
       <c r="BO8">
         <v>37271.404396038197</v>
       </c>
+      <c r="BP8" t="s">
+        <v>908</v>
+      </c>
       <c r="BQ8" t="s">
         <v>806</v>
       </c>
@@ -10836,6 +11021,9 @@
       <c r="BO34">
         <v>21697.693711266202</v>
       </c>
+      <c r="BP34" t="s">
+        <v>907</v>
+      </c>
       <c r="BQ34" t="s">
         <v>827</v>
       </c>
@@ -17862,6 +18050,9 @@
       <c r="BO67">
         <v>31441.188131695999</v>
       </c>
+      <c r="BP67" t="s">
+        <v>909</v>
+      </c>
       <c r="BQ67" t="s">
         <v>851</v>
       </c>
@@ -19350,6 +19541,9 @@
       <c r="BO74">
         <v>46631.566543654902</v>
       </c>
+      <c r="BP74" t="s">
+        <v>903</v>
+      </c>
       <c r="BQ74" t="s">
         <v>857</v>
       </c>
@@ -23181,6 +23375,9 @@
       <c r="BO92">
         <v>41989.8511217462</v>
       </c>
+      <c r="BP92" t="s">
+        <v>902</v>
+      </c>
       <c r="BQ92" t="s">
         <v>871</v>
       </c>
@@ -24456,6 +24653,9 @@
       <c r="BO98">
         <v>32043.933358929298</v>
       </c>
+      <c r="BP98" t="s">
+        <v>901</v>
+      </c>
       <c r="BQ98" t="s">
         <v>871</v>
       </c>
@@ -26796,6 +26996,9 @@
       <c r="BO109">
         <v>26916.926232279598</v>
       </c>
+      <c r="BP109" t="s">
+        <v>904</v>
+      </c>
       <c r="BQ109" t="s">
         <v>883</v>
       </c>
@@ -29775,6 +29978,9 @@
       <c r="BO123">
         <v>5072.7224186308204</v>
       </c>
+      <c r="BP123" t="s">
+        <v>905</v>
+      </c>
       <c r="BQ123" t="s">
         <v>891</v>
       </c>
@@ -31050,6 +31256,9 @@
       <c r="BO129">
         <v>22266.861089464299</v>
       </c>
+      <c r="BP129" t="s">
+        <v>906</v>
+      </c>
       <c r="BQ129" t="s">
         <v>893</v>
       </c>
@@ -34042,5 +34251,8 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>